--- a/data/trans_camb/CAGE_R-Edad-trans_camb.xlsx
+++ b/data/trans_camb/CAGE_R-Edad-trans_camb.xlsx
@@ -523,7 +523,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con consumo de riesgo, consumo perudicial o dependencia al alcohol (CAGE)</t>
+          <t>Población con consumo de riesgo, consumo perjudicial o dependencia al alcohol (CAGE)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,02; 3,82</t>
+          <t>0,18; 3,91</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-1,36; 1,65</t>
+          <t>-1,46; 1,74</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-2,73; -0,35</t>
+          <t>-2,66; -0,4</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-0,93; 1,45</t>
+          <t>-0,98; 1,44</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-1,23; 1,22</t>
+          <t>-1,24; 1,13</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-0,31; 12,4</t>
+          <t>-0,4; 11,2</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,01; 2,32</t>
+          <t>0,03; 2,26</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-0,82; 1,24</t>
+          <t>-0,98; 1,04</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-0,76; 4,35</t>
+          <t>-0,94; 4,25</t>
         </is>
       </c>
     </row>
@@ -783,22 +783,22 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-14,05; 680,07</t>
+          <t>-10,14; 644,03</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-78,9; 303,2</t>
+          <t>-82,85; 280,86</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 1,83</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 731,01</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -813,17 +813,17 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-10,9; 415,67</t>
+          <t>-10,41; 359,27</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-59,61; 225,84</t>
+          <t>-69,12; 198,82</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-87,49; 1082,74</t>
+          <t>-90,3; 740,35</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,04; 2,72</t>
+          <t>0,09; 2,71</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,27; 3,37</t>
+          <t>0,17; 3,19</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,05; 7,12</t>
+          <t>-0,07; 7,04</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,72; 0,0</t>
+          <t>-1,45; 0,0</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-0,52; 1,38</t>
+          <t>-0,56; 1,37</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-0,7; 2,46</t>
+          <t>-0,72; 2,5</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-0,24; 1,23</t>
+          <t>-0,31; 1,14</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,23; 2,04</t>
+          <t>0,19; 1,95</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,07; 3,99</t>
+          <t>-0,0; 4,3</t>
         </is>
       </c>
     </row>
@@ -999,17 +999,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-12,43; 692,98</t>
+          <t>-13,17; 623,32</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-8,5; 766,59</t>
+          <t>3,02; 730,96</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-40,44; 1478,2</t>
+          <t>-30,82; 1634,44</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1029,17 +1029,17 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-32,33; 343,39</t>
+          <t>-35,96; 313,89</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>4,17; 567,44</t>
+          <t>-2,11; 489,85</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-11,56; 1019,98</t>
+          <t>-24,63; 1082,12</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,02; 2,43</t>
+          <t>-0,05; 2,62</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-0,63; 1,58</t>
+          <t>-0,6; 1,54</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,58; 2,47</t>
+          <t>-0,65; 2,7</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-0,6; 0,0</t>
+          <t>-0,84; 0,0</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-0,32; 0,57</t>
+          <t>-0,35; 0,55</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,02; 3,7</t>
+          <t>0,14; 3,5</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-0,1; 1,14</t>
+          <t>-0,04; 1,16</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-0,25; 0,94</t>
+          <t>-0,26; 0,9</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,08; 2,36</t>
+          <t>0,08; 2,2</t>
         </is>
       </c>
     </row>
@@ -1215,17 +1215,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-22,2; 727,98</t>
+          <t>-20,98; 978,37</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-60,54; 487,8</t>
+          <t>-60,02; 428,58</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-74,89; 881,78</t>
+          <t>-82,15; 1178,08</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -1245,17 +1245,17 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-32,89; 599,5</t>
+          <t>-17,41; 667,94</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-48,69; 511,6</t>
+          <t>-46,45; 492,09</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-11,74; 1049,73</t>
+          <t>-14,26; 1184,99</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,88; 3,81</t>
+          <t>1,0; 3,85</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,69; 3,04</t>
+          <t>0,7; 3,16</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,66; 3,63</t>
+          <t>0,69; 3,8</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1,08; 0,0</t>
+          <t>-1,14; 0,0</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-0,46; 1,03</t>
+          <t>-0,35; 1,03</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-0,11; 2,64</t>
+          <t>0,0; 3,09</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,32; 1,75</t>
+          <t>0,35; 1,9</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,32; 1,77</t>
+          <t>0,39; 1,66</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,63; 2,68</t>
+          <t>0,6; 2,83</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-2,79; 0,97</t>
+          <t>-2,69; 0,83</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-2,24; 1,74</t>
+          <t>-2,13; 1,85</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-0,03; 5,7</t>
+          <t>0,29; 5,6</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-0,99; 0,45</t>
+          <t>-1,01; 0,45</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-0,51; 1,65</t>
+          <t>-0,51; 1,62</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,67; 5,28</t>
+          <t>0,73; 5,38</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-1,41; 0,58</t>
+          <t>-1,5; 0,47</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-0,87; 1,28</t>
+          <t>-0,87; 1,2</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>1,14; 4,78</t>
+          <t>1,11; 4,56</t>
         </is>
       </c>
     </row>
@@ -1647,17 +1647,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-94,48; 203,15</t>
+          <t>-92,45; 245,5</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-75,85; 200,98</t>
+          <t>-74,67; 238,94</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-14,65; 627,0</t>
+          <t>-8,54; 533,68</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -1677,17 +1677,17 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-89,25; 167,1</t>
+          <t>-90,16; 114,69</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-63,56; 221,36</t>
+          <t>-60,05; 212,98</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>49,21; 806,8</t>
+          <t>48,77; 851,72</t>
         </is>
       </c>
     </row>
@@ -1757,17 +1757,17 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>0,33; 3,96</t>
+          <t>0,33; 3,97</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,57</t>
+          <t>0,0; 1,63</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>0,9; 4,46</t>
+          <t>0,96; 4,34</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
@@ -1777,27 +1777,27 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,69</t>
+          <t>0,0; 1,44</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,24</t>
+          <t>0,0; 1,27</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>0,15; 2,08</t>
+          <t>0,15; 2,07</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,87</t>
+          <t>0,0; 0,97</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>0,16; 2,41</t>
+          <t>0,16; 2,38</t>
         </is>
       </c>
     </row>
@@ -1973,17 +1973,17 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-0,96; 3,2</t>
+          <t>-0,95; 3,66</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-1,95; 0,71</t>
+          <t>-1,93; 0,71</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,44</t>
+          <t>0,0; 5,25</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
@@ -1998,22 +1998,22 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,18</t>
+          <t>0,0; 7,6</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-0,37; 1,47</t>
+          <t>-0,37; 1,43</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-0,72; 0,28</t>
+          <t>-0,73; 0,28</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>0,44; 4,63</t>
+          <t>0,52; 4,72</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>0,57; 1,77</t>
+          <t>0,63; 1,79</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>0,17; 1,21</t>
+          <t>0,16; 1,24</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>0,72; 2,35</t>
+          <t>0,74; 2,45</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-0,38; 0,08</t>
+          <t>-0,4; 0,07</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-0,09; 0,51</t>
+          <t>-0,11; 0,49</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>0,28; 1,98</t>
+          <t>0,22; 2,03</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>0,19; 0,84</t>
+          <t>0,17; 0,78</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>0,13; 0,75</t>
+          <t>0,11; 0,72</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>0,77; 2,01</t>
+          <t>0,64; 1,93</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>48,48; 305,79</t>
+          <t>58,31; 310,93</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>13,79; 219,2</t>
+          <t>10,24; 200,54</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>72,37; 400,91</t>
+          <t>75,12; 409,43</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-88,23; 84,49</t>
+          <t>-88,11; 85,72</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-30,01; 337,74</t>
+          <t>-37,4; 312,52</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>63,17; 1178,94</t>
+          <t>50,07; 1035,17</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>28,22; 208,48</t>
+          <t>25,21; 201,8</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>16,83; 188,71</t>
+          <t>17,59; 189,01</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>126,35; 497,5</t>
+          <t>110,68; 455,96</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/CAGE_R-Edad-trans_camb.xlsx
+++ b/data/trans_camb/CAGE_R-Edad-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>-1,18</t>
+          <t>-0,28</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,31</t>
+          <t>4,84</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>0,54</t>
+          <t>1,82</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,18; 3,91</t>
+          <t>0,04; 3,89</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-1,46; 1,74</t>
+          <t>-1,46; 1,96</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-2,66; -0,4</t>
+          <t>-1,87; 3,27</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-0,98; 1,44</t>
+          <t>-0,95; 1,57</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-1,24; 1,13</t>
+          <t>-1,12; 1,11</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-0,4; 11,2</t>
+          <t>0,65; 13,47</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,03; 2,26</t>
+          <t>0,02; 2,33</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-0,98; 1,04</t>
+          <t>-0,94; 1,12</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-0,94; 4,25</t>
+          <t>-0,19; 6,3</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>-92,38%</t>
+          <t>-21,86%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>456,44%</t>
+          <t>666,96%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>53,83%</t>
+          <t>180,57%</t>
         </is>
       </c>
     </row>
@@ -783,22 +783,22 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-10,14; 644,03</t>
+          <t>-7,92; 684,41</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-82,85; 280,86</t>
+          <t>-82,11; 406,66</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 1,83</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 731,01</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -813,17 +813,17 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-10,41; 359,27</t>
+          <t>-2,88; 453,74</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-69,12; 198,82</t>
+          <t>-65,6; 229,76</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-90,3; 740,35</t>
+          <t>-42,01; 909,78</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2,31</t>
+          <t>2,35</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,18</t>
+          <t>0,14</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>1,54</t>
+          <t>1,55</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,09; 2,71</t>
+          <t>0,1; 2,58</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,17; 3,19</t>
+          <t>0,16; 3,04</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,07; 7,04</t>
+          <t>0,21; 6,69</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,45; 0,0</t>
+          <t>-1,41; 0,0</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-0,56; 1,37</t>
+          <t>-0,52; 1,45</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-0,72; 2,5</t>
+          <t>-0,66; 2,27</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-0,31; 1,14</t>
+          <t>-0,29; 1,21</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,19; 1,95</t>
+          <t>0,24; 1,98</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-0,0; 4,3</t>
+          <t>0,07; 4,13</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>269,69%</t>
+          <t>273,79%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>42,4%</t>
+          <t>32,85%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>233,09%</t>
+          <t>234,67%</t>
         </is>
       </c>
     </row>
@@ -999,17 +999,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-13,17; 623,32</t>
+          <t>-16,97; 628,17</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>3,02; 730,96</t>
+          <t>0,45; 659,06</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-30,82; 1634,44</t>
+          <t>-16,93; 1347,78</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; —</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1029,17 +1029,17 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-35,96; 313,89</t>
+          <t>-33,69; 347,75</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-2,11; 489,85</t>
+          <t>10,19; 572,77</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-24,63; 1082,12</t>
+          <t>-12,4; 1117,71</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0,54</t>
+          <t>1,08</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,15</t>
+          <t>1,09</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0,86</t>
+          <t>1,18</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,05; 2,62</t>
+          <t>0,05; 2,54</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-0,6; 1,54</t>
+          <t>-0,56; 1,53</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,65; 2,7</t>
+          <t>-0,38; 3,31</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-0,84; 0,0</t>
+          <t>-0,74; 0,0</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-0,35; 0,55</t>
+          <t>-0,32; 0,65</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,14; 3,5</t>
+          <t>0,0; 3,17</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-0,04; 1,16</t>
+          <t>-0,07; 1,19</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-0,26; 0,9</t>
+          <t>-0,25; 0,91</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,08; 2,2</t>
+          <t>0,17; 2,66</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>70,79%</t>
+          <t>141,81%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>781,45%</t>
+          <t>736,44%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>193,86%</t>
+          <t>267,74%</t>
         </is>
       </c>
     </row>
@@ -1215,17 +1215,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-20,98; 978,37</t>
+          <t>-4,72; 756,62</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-60,02; 428,58</t>
+          <t>-52,9; 667,78</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-82,15; 1178,08</t>
+          <t>-56,94; 954,83</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -1245,17 +1245,17 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-17,41; 667,94</t>
+          <t>-20,39; 568,45</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-46,45; 492,09</t>
+          <t>-48,8; 417,95</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-14,26; 1184,99</t>
+          <t>-5,77; 949,4</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1,79</t>
+          <t>1,98</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,22 +1297,22 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
+          <t>1,13</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
           <t>0,92</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
+      <c r="J16" s="2" t="inlineStr">
         <is>
           <t>0,92</t>
         </is>
       </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>0,92</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>1,45</t>
+          <t>1,63</t>
         </is>
       </c>
     </row>
@@ -1325,17 +1325,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1,0; 3,85</t>
+          <t>1,01; 4,0</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,7; 3,16</t>
+          <t>0,76; 2,91</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,69; 3,8</t>
+          <t>0,84; 3,85</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -1345,27 +1345,27 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-0,35; 1,03</t>
+          <t>-0,45; 1,03</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,09</t>
+          <t>0,02; 2,85</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,35; 1,9</t>
+          <t>0,31; 1,8</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,39; 1,66</t>
+          <t>0,36; 1,75</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,6; 2,83</t>
+          <t>0,77; 3,0</t>
         </is>
       </c>
     </row>
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>404,4%</t>
+          <t>496,88%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>1280,18%</t>
+          <t>1440,28%</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>2,6</t>
+          <t>2,29</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>2,37</t>
+          <t>2,32</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>2,8</t>
+          <t>2,57</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-2,69; 0,83</t>
+          <t>-2,72; 0,93</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-2,13; 1,85</t>
+          <t>-1,96; 1,84</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0,29; 5,6</t>
+          <t>-0,14; 5,05</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-1,01; 0,45</t>
+          <t>-0,77; 0,45</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-0,51; 1,62</t>
+          <t>-0,51; 1,54</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,73; 5,38</t>
+          <t>0,75; 5,29</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-1,5; 0,47</t>
+          <t>-1,44; 0,51</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-0,87; 1,2</t>
+          <t>-1,01; 1,23</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>1,11; 4,56</t>
+          <t>0,92; 4,34</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>139,94%</t>
+          <t>123,55%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>931,17%</t>
+          <t>910,59%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>269,45%</t>
+          <t>247,24%</t>
         </is>
       </c>
     </row>
@@ -1647,17 +1647,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-92,45; 245,5</t>
+          <t>-100,0; 158,81</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-74,67; 238,94</t>
+          <t>-72,48; 218,02</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-8,54; 533,68</t>
+          <t>-23,98; 550,93</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -1677,17 +1677,17 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-90,16; 114,69</t>
+          <t>-89,41; 232,99</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-60,05; 212,98</t>
+          <t>-66,43; 228,72</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>48,77; 851,72</t>
+          <t>23,57; 738,89</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>2,11</t>
+          <t>2,35</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0,16</t>
+          <t>0,58</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>0,95</t>
+          <t>1,86</t>
         </is>
       </c>
     </row>
@@ -1757,17 +1757,17 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>0,33; 3,97</t>
+          <t>0,6; 4,23</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,63</t>
+          <t>0,0; 1,44</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>0,96; 4,34</t>
+          <t>0,95; 4,57</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
@@ -1777,27 +1777,27 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,44</t>
+          <t>0,0; 1,43</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,27</t>
+          <t>0,0; 2,4</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>0,15; 2,07</t>
+          <t>0,28; 1,96</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,97</t>
+          <t>0,0; 1,0</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>0,16; 2,38</t>
+          <t>0,87; 3,63</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1,9</t>
+          <t>1,75</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1,52</t>
+          <t>1,43</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>2,02</t>
+          <t>1,87</t>
         </is>
       </c>
     </row>
@@ -1973,17 +1973,17 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-0,95; 3,66</t>
+          <t>-0,95; 3,63</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-1,93; 0,71</t>
+          <t>-1,94; 0,71</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,25</t>
+          <t>0,01; 4,92</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
@@ -1998,22 +1998,22 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,6</t>
+          <t>0,0; 7,45</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-0,37; 1,43</t>
+          <t>-0,37; 1,44</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-0,73; 0,28</t>
+          <t>-0,6; 0,28</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>0,52; 4,72</t>
+          <t>0,38; 4,52</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>396,63%</t>
+          <t>365,04%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>1088,84%</t>
+          <t>1011,91%</t>
         </is>
       </c>
     </row>
@@ -2146,7 +2146,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>1,46</t>
+          <t>1,68</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -2161,7 +2161,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>1,04</t>
+          <t>1,58</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>1,35</t>
+          <t>1,73</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>0,63; 1,79</t>
+          <t>0,56; 1,73</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>0,16; 1,24</t>
+          <t>0,18; 1,2</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>0,74; 2,45</t>
+          <t>0,9; 2,54</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-0,4; 0,07</t>
+          <t>-0,42; 0,09</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-0,11; 0,49</t>
+          <t>-0,09; 0,54</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>0,22; 2,03</t>
+          <t>0,79; 2,85</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>0,17; 0,78</t>
+          <t>0,2; 0,8</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>0,11; 0,72</t>
+          <t>0,11; 0,71</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>0,64; 1,93</t>
+          <t>1,16; 2,39</t>
         </is>
       </c>
     </row>
@@ -2252,7 +2252,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>186,74%</t>
+          <t>214,75%</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>377,6%</t>
+          <t>575,65%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>257,9%</t>
+          <t>329,07%</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>58,31; 310,93</t>
+          <t>55,08; 312,55</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>10,24; 200,54</t>
+          <t>16,13; 212,68</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>75,12; 409,43</t>
+          <t>84,5; 436,34</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-88,11; 85,72</t>
+          <t>-88,23; 99,41</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-37,4; 312,52</t>
+          <t>-30,8; 367,24</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>50,07; 1035,17</t>
+          <t>143,35; 1685,86</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>25,21; 201,8</t>
+          <t>27,97; 197,99</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>17,59; 189,01</t>
+          <t>16,44; 184,63</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>110,68; 455,96</t>
+          <t>167,37; 560,9</t>
         </is>
       </c>
     </row>
